--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2015_T2_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2015_T2_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>94</t>
+    <t>90</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.661</t>
-  </si>
-  <si>
-    <t>(0.077)</t>
-  </si>
-  <si>
-    <t>4.415</t>
-  </si>
-  <si>
-    <t>(0.536)</t>
-  </si>
-  <si>
-    <t>13.576</t>
-  </si>
-  <si>
-    <t>(2.510)</t>
-  </si>
-  <si>
-    <t>17.825</t>
-  </si>
-  <si>
-    <t>(2.851)</t>
-  </si>
-  <si>
-    <t>1.377</t>
-  </si>
-  <si>
-    <t>(0.294)</t>
-  </si>
-  <si>
-    <t>7.553</t>
-  </si>
-  <si>
-    <t>(0.810)</t>
-  </si>
-  <si>
-    <t>1.467</t>
-  </si>
-  <si>
-    <t>(0.278)</t>
-  </si>
-  <si>
-    <t>0.744</t>
-  </si>
-  <si>
-    <t>(0.228)</t>
-  </si>
-  <si>
-    <t>24.004</t>
-  </si>
-  <si>
-    <t>(4.008)</t>
-  </si>
-  <si>
-    <t>11.092</t>
-  </si>
-  <si>
-    <t>(1.492)</t>
+    <t>0.690</t>
+  </si>
+  <si>
+    <t>(0.079)</t>
+  </si>
+  <si>
+    <t>4.611</t>
+  </si>
+  <si>
+    <t>(0.551)</t>
+  </si>
+  <si>
+    <t>12.168</t>
+  </si>
+  <si>
+    <t>(1.867)</t>
+  </si>
+  <si>
+    <t>16.235</t>
+  </si>
+  <si>
+    <t>(2.244)</t>
+  </si>
+  <si>
+    <t>1.438</t>
+  </si>
+  <si>
+    <t>(0.306)</t>
+  </si>
+  <si>
+    <t>7.889</t>
+  </si>
+  <si>
+    <t>(0.828)</t>
+  </si>
+  <si>
+    <t>1.356</t>
+  </si>
+  <si>
+    <t>(0.248)</t>
+  </si>
+  <si>
+    <t>0.583</t>
+  </si>
+  <si>
+    <t>(0.173)</t>
+  </si>
+  <si>
+    <t>21.480</t>
+  </si>
+  <si>
+    <t>(3.034)</t>
+  </si>
+  <si>
+    <t>11.117</t>
+  </si>
+  <si>
+    <t>(1.512)</t>
   </si>
   <si>
     <t>20</t>
@@ -198,7 +198,7 @@
     <t>(9.870)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.549*</t>
-  </si>
-  <si>
-    <t>-0.715</t>
-  </si>
-  <si>
-    <t>35.502***</t>
-  </si>
-  <si>
-    <t>36.995***</t>
-  </si>
-  <si>
-    <t>-0.285</t>
-  </si>
-  <si>
-    <t>-3.703**</t>
-  </si>
-  <si>
-    <t>1.417**</t>
-  </si>
-  <si>
-    <t>-0.188</t>
-  </si>
-  <si>
-    <t>43.957***</t>
-  </si>
-  <si>
-    <t>31.334***</t>
+    <t>0.519*</t>
+  </si>
+  <si>
+    <t>-0.911</t>
+  </si>
+  <si>
+    <t>36.910***</t>
+  </si>
+  <si>
+    <t>38.585***</t>
+  </si>
+  <si>
+    <t>-0.346</t>
+  </si>
+  <si>
+    <t>-4.039**</t>
+  </si>
+  <si>
+    <t>1.528***</t>
+  </si>
+  <si>
+    <t>-0.027</t>
+  </si>
+  <si>
+    <t>46.481***</t>
+  </si>
+  <si>
+    <t>31.309***</t>
   </si>
 </sst>
 </file>
